--- a/EKG_Kalite_Yönetim_Sistemi/13_Giriş Lojistiği ve Depolama/03_ILG3 - Depolama, FIFO ve Raf Ömrü/EKG-LOJ-MTR-02_depolama_ve_ic_tasima_denetim_ve_risk_matrisi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/13_Giriş Lojistiği ve Depolama/03_ILG3 - Depolama, FIFO ve Raf Ömrü/EKG-LOJ-MTR-02_depolama_ve_ic_tasima_denetim_ve_risk_matrisi.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yürürlük Tarihi: 04.05.2026</t>
+          <t xml:space="preserve">Yürürlük Tarihi: 03.06.2026</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-MTR-02&amp;C&amp;"Arial,Regular"&amp;11Depolama ve İç Taşıma Denetim ve Risk Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 07.09.2026
+Revizyon nedeni: Ortam formülleri onaylı limit girdilerine bağlandı; eksik ve ters kriter uyarıları eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1240,7 +1241,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-MTR-02&amp;C&amp;"Arial,Regular"&amp;11Depolama ve İç Taşıma Denetim ve Risk Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 07.09.2026
+Revizyon nedeni: Ortam formülleri onaylı limit girdilerine bağlandı; eksik ve ters kriter uyarıları eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>